--- a/游戏设计王/老虎机数学入门-PartIV-WayGame模型.xlsx
+++ b/游戏设计王/老虎机数学入门-PartIV-WayGame模型.xlsx
@@ -802,13 +802,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -1531,7 +1532,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1590,6 +1591,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -18176,7 +18180,7 @@
         <f>PRODUCT(3*($B$38+$B$39),3*($C$38+$C$39),3*($D$38+$D$39),3*($E$38+$E$39),3*($F$38+$F$39))</f>
         <v>124416</v>
       </c>
-      <c r="E78" s="17">
+      <c r="E78" s="38">
         <f t="shared" ref="E78:E108" si="6">D78/$B$74</f>
         <v>0.03888</v>
       </c>
@@ -18257,7 +18261,7 @@
         <f>PRODUCT(3*($B$38+$B$39),3*($C$38+$C$39),3*($D$38+$D$39),3*($E$38+$E$39),($F$35-$BA$71))</f>
         <v>103680</v>
       </c>
-      <c r="E79" s="17">
+      <c r="E79" s="38">
         <f t="shared" si="6"/>
         <v>0.0324</v>
       </c>
@@ -18338,7 +18342,7 @@
         <f>PRODUCT(3*($B$38+$B$39),3*($C$38+$C$39),3*($D$38+$D$39),($E$35-$AO$71),$F$35)</f>
         <v>172800</v>
       </c>
-      <c r="E80" s="17">
+      <c r="E80" s="38">
         <f t="shared" si="6"/>
         <v>0.054</v>
       </c>
@@ -18419,7 +18423,7 @@
         <f>PRODUCT(3*($B$38+$B$40),3*($C$38+$C$40),3*($D$38+$D$40),3*($E$38+$E$40),3*($F$38+$F$40))</f>
         <v>186624</v>
       </c>
-      <c r="E81" s="17">
+      <c r="E81" s="38">
         <f t="shared" si="6"/>
         <v>0.05832</v>
       </c>
@@ -18500,7 +18504,7 @@
         <f>PRODUCT(3*($B$38+$B$40),3*($C$38+$C$40),3*($D$38+$D$40),3*($E$38+$E$40),($F$35-$BC$71))</f>
         <v>139968</v>
       </c>
-      <c r="E82" s="17">
+      <c r="E82" s="38">
         <f t="shared" si="6"/>
         <v>0.04374</v>
       </c>
@@ -18581,7 +18585,7 @@
         <f>PRODUCT(3*($B$38+$B$40),3*($C$38+$C$40),3*($D$38+$D$40),($E$35-$AQ$71),$F$35)</f>
         <v>233280</v>
       </c>
-      <c r="E83" s="17">
+      <c r="E83" s="38">
         <f t="shared" si="6"/>
         <v>0.0729</v>
       </c>
@@ -18662,7 +18666,7 @@
         <f>PRODUCT(3*($B$38+$B$41),3*($C$38+$C$41),3*($D$38+$D$41),3*($E$38+$E$41),3*($F$38+$F$41))</f>
         <v>729000</v>
       </c>
-      <c r="E84" s="17">
+      <c r="E84" s="38">
         <f t="shared" si="6"/>
         <v>0.2278125</v>
       </c>
@@ -18743,7 +18747,7 @@
         <f>PRODUCT(3*($B$38+$B$41),3*($C$38+$C$41),3*($D$38+$D$41),3*($E$38+$E$41),($F$35-$BE$71))</f>
         <v>243000</v>
       </c>
-      <c r="E85" s="17">
+      <c r="E85" s="38">
         <f t="shared" si="6"/>
         <v>0.0759375</v>
       </c>
@@ -18824,7 +18828,7 @@
         <f>PRODUCT(3*($B$38+$B$41),3*($C$38+$C$41),3*($D$38+$D$41),($E$35-$AS$71),$F$35)</f>
         <v>324000</v>
       </c>
-      <c r="E86" s="17">
+      <c r="E86" s="38">
         <f t="shared" si="6"/>
         <v>0.10125</v>
       </c>
@@ -18905,7 +18909,7 @@
         <f>PRODUCT(3*($B$38+$B$42),3*($C$38+$C$42),3*($D$38+$D$42),3*($E$38+$E$42),3*($F$38+$F$42))</f>
         <v>607500</v>
       </c>
-      <c r="E87" s="17">
+      <c r="E87" s="38">
         <f t="shared" si="6"/>
         <v>0.18984375</v>
       </c>
@@ -18986,7 +18990,7 @@
         <f>PRODUCT(3*($B$38+$B$42),3*($C$38+$C$42),3*($D$38+$D$42),3*($E$38+$E$42),($F$35-$BG$71))</f>
         <v>243000</v>
       </c>
-      <c r="E88" s="17">
+      <c r="E88" s="38">
         <f t="shared" si="6"/>
         <v>0.0759375</v>
       </c>
@@ -19067,7 +19071,7 @@
         <f>PRODUCT(3*($B$38+$B$42),3*($C$38+$C$42),3*($D$38+$D$42),($E$35-$AU$71),$F$35)</f>
         <v>324000</v>
       </c>
-      <c r="E89" s="17">
+      <c r="E89" s="38">
         <f t="shared" si="6"/>
         <v>0.10125</v>
       </c>
@@ -19148,7 +19152,7 @@
         <f>PRODUCT(3*($B$38+$B$43),3*($C$38+$C$43),3*($D$38+$D$43),3*($E$38+$E$43),3*($F$38+$F$43))</f>
         <v>1093500</v>
       </c>
-      <c r="E90" s="17">
+      <c r="E90" s="38">
         <f t="shared" si="6"/>
         <v>0.34171875</v>
       </c>
@@ -19229,7 +19233,7 @@
         <f>PRODUCT(3*($B$38+$B$43),3*($C$38+$C$43),3*($D$38+$D$43),3*($E$38+$E$43),($F$35-$BI$71))</f>
         <v>364500</v>
       </c>
-      <c r="E91" s="17">
+      <c r="E91" s="38">
         <f t="shared" si="6"/>
         <v>0.11390625</v>
       </c>
@@ -19310,7 +19314,7 @@
         <f>PRODUCT(3*($B$38+$B$43),3*($C$38+$C$43),3*($D$38+$D$43),($E$35-$AW$71),$F$35)</f>
         <v>567000</v>
       </c>
-      <c r="E92" s="17">
+      <c r="E92" s="38">
         <f t="shared" si="6"/>
         <v>0.1771875</v>
       </c>
@@ -19391,7 +19395,7 @@
         <f>(($BK$71*$BL$71*$BM$71+$BK$71*$BL$71*$BN$71+$BK$71*$BM$71*$BN$71+$BL$71*$BM$71*$BN$71)*$B$35*$B$35)-(3*$BK$71*$BL$71*$BM$71*$BN$71*$B$35)</f>
         <v>10800</v>
       </c>
-      <c r="E93" s="17">
+      <c r="E93" s="38">
         <f t="shared" si="6"/>
         <v>0.003375</v>
       </c>
